--- a/Модель PIVOT.xlsx
+++ b/Модель PIVOT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\world\Desktop\MARSIntMap\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A078138-7778-4803-8BA0-B72DC5423EC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16769535-2AF3-4D5E-A873-67694A917D45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="8" xr2:uid="{557A26C6-F21E-4F13-8F97-2AB80881C4B7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{557A26C6-F21E-4F13-8F97-2AB80881C4B7}"/>
   </bookViews>
   <sheets>
     <sheet name="Пример" sheetId="1" r:id="rId1"/>
@@ -51548,6 +51548,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7BCE706-FAD7-4CD7-B4ED-991E63946BE0}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AX68"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -51875,7 +51876,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="4" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>412</v>
       </c>
@@ -52106,7 +52107,7 @@
       <c r="AP5" s="224"/>
       <c r="AQ5" s="218"/>
     </row>
-    <row r="6" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>418</v>
       </c>
@@ -52207,7 +52208,7 @@
       <c r="AP6" s="224"/>
       <c r="AQ6" s="218"/>
     </row>
-    <row r="7" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>420</v>
       </c>
@@ -52308,7 +52309,7 @@
       <c r="AP7" s="224"/>
       <c r="AQ7" s="218"/>
     </row>
-    <row r="8" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>421</v>
       </c>
@@ -52409,7 +52410,7 @@
       <c r="AP8" s="224"/>
       <c r="AQ8" s="218"/>
     </row>
-    <row r="9" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>421</v>
       </c>
@@ -52516,7 +52517,7 @@
       <c r="AP9" s="224"/>
       <c r="AQ9" s="218"/>
     </row>
-    <row r="10" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>420</v>
       </c>
@@ -52620,7 +52621,7 @@
       <c r="AP10" s="239"/>
       <c r="AQ10" s="218"/>
     </row>
-    <row r="11" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>423</v>
       </c>
@@ -52943,7 +52944,7 @@
       <c r="AP13" s="224"/>
       <c r="AQ13" s="218"/>
     </row>
-    <row r="14" spans="1:50" s="239" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:50" s="239" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>428</v>
       </c>
@@ -53054,7 +53055,7 @@
       <c r="AP14" s="224"/>
       <c r="AQ14" s="218"/>
     </row>
-    <row r="15" spans="1:50" s="239" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:50" s="239" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>429</v>
       </c>
@@ -53163,7 +53164,7 @@
       <c r="AP15" s="224"/>
       <c r="AQ15" s="218"/>
     </row>
-    <row r="16" spans="1:50" s="239" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:50" s="239" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>429</v>
       </c>
@@ -53490,7 +53491,7 @@
       <c r="AP18" s="224"/>
       <c r="AQ18" s="218"/>
     </row>
-    <row r="19" spans="1:43" s="239" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:43" s="239" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>430</v>
       </c>
@@ -53599,7 +53600,7 @@
       <c r="AP19" s="224"/>
       <c r="AQ19" s="218"/>
     </row>
-    <row r="20" spans="1:43" s="239" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:43" s="239" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>432</v>
       </c>
@@ -53706,7 +53707,7 @@
       <c r="AP20" s="224"/>
       <c r="AQ20" s="218"/>
     </row>
-    <row r="21" spans="1:43" s="239" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:43" s="239" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>432</v>
       </c>
@@ -53812,7 +53813,7 @@
       <c r="AO21"/>
       <c r="AQ21" s="218"/>
     </row>
-    <row r="22" spans="1:43" s="239" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:43" s="239" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>432</v>
       </c>
@@ -53921,7 +53922,7 @@
       <c r="AP22" s="224"/>
       <c r="AQ22" s="218"/>
     </row>
-    <row r="23" spans="1:43" s="239" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:43" s="239" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>432</v>
       </c>
@@ -54028,7 +54029,7 @@
       <c r="AP23" s="224"/>
       <c r="AQ23" s="218"/>
     </row>
-    <row r="24" spans="1:43" s="239" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:43" s="239" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>432</v>
       </c>
@@ -54246,7 +54247,7 @@
       <c r="AP25" s="224"/>
       <c r="AQ25" s="218"/>
     </row>
-    <row r="26" spans="1:43" s="239" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:43" s="239" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>433</v>
       </c>
@@ -54464,7 +54465,7 @@
       <c r="AP27" s="224"/>
       <c r="AQ27" s="218"/>
     </row>
-    <row r="28" spans="1:43" s="239" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:43" s="239" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>435</v>
       </c>
@@ -54573,7 +54574,7 @@
       <c r="AP28" s="224"/>
       <c r="AQ28" s="218"/>
     </row>
-    <row r="29" spans="1:43" s="239" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:43" s="239" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>435</v>
       </c>
@@ -54791,7 +54792,7 @@
       <c r="AP30" s="224"/>
       <c r="AQ30" s="218"/>
     </row>
-    <row r="31" spans="1:43" s="239" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:43" s="239" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>433</v>
       </c>
@@ -54900,7 +54901,7 @@
       <c r="AP31" s="224"/>
       <c r="AQ31" s="218"/>
     </row>
-    <row r="32" spans="1:43" s="239" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:43" s="239" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>433</v>
       </c>
@@ -55204,7 +55205,7 @@
       <c r="AO34"/>
       <c r="AQ34" s="218"/>
     </row>
-    <row r="35" spans="1:43" s="239" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:43" s="239" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>242</v>
       </c>
@@ -55296,7 +55297,7 @@
       <c r="AO35"/>
       <c r="AQ35" s="218"/>
     </row>
-    <row r="36" spans="1:43" s="239" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:43" s="239" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>418</v>
       </c>
@@ -55401,7 +55402,7 @@
       <c r="AP36" s="224"/>
       <c r="AQ36" s="218"/>
     </row>
-    <row r="37" spans="1:43" s="239" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:43" s="239" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>432</v>
       </c>
@@ -55615,7 +55616,7 @@
       <c r="AP38" s="224"/>
       <c r="AQ38" s="218"/>
     </row>
-    <row r="39" spans="1:43" s="239" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:43" s="239" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>191</v>
       </c>
@@ -55724,7 +55725,7 @@
       <c r="AP39" s="224"/>
       <c r="AQ39" s="218"/>
     </row>
-    <row r="40" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>191</v>
       </c>
@@ -55825,7 +55826,7 @@
       <c r="AP40" s="224"/>
       <c r="AQ40" s="218"/>
     </row>
-    <row r="41" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>438</v>
       </c>
@@ -55926,7 +55927,7 @@
       <c r="AP41" s="224"/>
       <c r="AQ41" s="218"/>
     </row>
-    <row r="42" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>438</v>
       </c>
@@ -56027,7 +56028,7 @@
       <c r="AP42" s="239"/>
       <c r="AQ42" s="218"/>
     </row>
-    <row r="43" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>412</v>
       </c>
@@ -56108,7 +56109,7 @@
       </c>
       <c r="AQ43" s="218"/>
     </row>
-    <row r="44" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>421</v>
       </c>
@@ -56187,7 +56188,7 @@
       <c r="AP44" s="224"/>
       <c r="AQ44" s="218"/>
     </row>
-    <row r="45" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>420</v>
       </c>
@@ -56271,7 +56272,7 @@
       </c>
       <c r="AQ45" s="218"/>
     </row>
-    <row r="46" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>429</v>
       </c>
@@ -56353,7 +56354,7 @@
       <c r="AP46" s="224"/>
       <c r="AQ46" s="218"/>
     </row>
-    <row r="47" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>430</v>
       </c>
@@ -56436,7 +56437,7 @@
       </c>
       <c r="AQ47" s="218"/>
     </row>
-    <row r="48" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>430</v>
       </c>
@@ -56517,7 +56518,7 @@
       </c>
       <c r="AQ48" s="218"/>
     </row>
-    <row r="49" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>434</v>
       </c>
@@ -56596,7 +56597,7 @@
       <c r="AP49" s="224"/>
       <c r="AQ49" s="218"/>
     </row>
-    <row r="50" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>434</v>
       </c>
@@ -56673,7 +56674,7 @@
       <c r="AP50" s="224"/>
       <c r="AQ50" s="218"/>
     </row>
-    <row r="51" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>436</v>
       </c>
@@ -56752,7 +56753,7 @@
       <c r="AP51" s="224"/>
       <c r="AQ51" s="218"/>
     </row>
-    <row r="52" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>433</v>
       </c>
@@ -56831,7 +56832,7 @@
       <c r="AP52" s="224"/>
       <c r="AQ52" s="218"/>
     </row>
-    <row r="53" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>426</v>
       </c>
@@ -56910,7 +56911,7 @@
       <c r="AP53" s="224"/>
       <c r="AQ53" s="218"/>
     </row>
-    <row r="54" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>428</v>
       </c>
@@ -56990,7 +56991,7 @@
       <c r="AP54" s="224"/>
       <c r="AQ54" s="218"/>
     </row>
-    <row r="55" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>242</v>
       </c>
@@ -57069,7 +57070,7 @@
       <c r="AP55" s="224"/>
       <c r="AQ55" s="218"/>
     </row>
-    <row r="56" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>418</v>
       </c>
@@ -57148,7 +57149,7 @@
       <c r="AP56" s="224"/>
       <c r="AQ56" s="218"/>
     </row>
-    <row r="57" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>432</v>
       </c>
@@ -57230,7 +57231,7 @@
       <c r="AP57" s="224"/>
       <c r="AQ57" s="218"/>
     </row>
-    <row r="58" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>438</v>
       </c>
@@ -57312,7 +57313,7 @@
       <c r="AP58" s="224"/>
       <c r="AQ58" s="218"/>
     </row>
-    <row r="59" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>430</v>
       </c>
@@ -57393,7 +57394,7 @@
       </c>
       <c r="AQ59" s="218"/>
     </row>
-    <row r="60" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>242</v>
       </c>
@@ -57470,7 +57471,7 @@
       <c r="AP60" s="224"/>
       <c r="AQ60" s="218"/>
     </row>
-    <row r="61" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>432</v>
       </c>
@@ -57546,7 +57547,7 @@
       <c r="AP61" s="239"/>
       <c r="AQ61" s="218"/>
     </row>
-    <row r="62" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>242</v>
       </c>
@@ -57622,7 +57623,7 @@
       <c r="AP62" s="224"/>
       <c r="AQ62" s="218"/>
     </row>
-    <row r="63" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>420</v>
       </c>
@@ -57832,7 +57833,7 @@
       <c r="AP65" s="224"/>
       <c r="AQ65" s="218"/>
     </row>
-    <row r="66" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>421</v>
       </c>
@@ -57905,7 +57906,7 @@
       <c r="AP66" s="224"/>
       <c r="AQ66" s="218"/>
     </row>
-    <row r="67" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>438</v>
       </c>
@@ -57975,7 +57976,7 @@
       <c r="AP67" s="224"/>
       <c r="AQ67" s="218"/>
     </row>
-    <row r="68" spans="1:43" s="246" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:43" s="246" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="246" t="s">
         <v>434</v>
       </c>
@@ -58053,7 +58054,14 @@
       <c r="AQ68" s="218"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:AP68" xr:uid="{F4E271B0-9BC6-43A9-829F-67EBEF38B757}"/>
+  <autoFilter ref="A3:AP68" xr:uid="{F4E271B0-9BC6-43A9-829F-67EBEF38B757}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="TSL NOR  SPb  North- Murmansk"/>
+        <filter val="TSL NOR Len Obl"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="9">
     <mergeCell ref="AR2:AS2"/>
     <mergeCell ref="AT2:AX2"/>

--- a/Модель PIVOT.xlsx
+++ b/Модель PIVOT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\world\Desktop\MARSIntMap\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16769535-2AF3-4D5E-A873-67694A917D45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CE0D520-96A7-4F32-821B-BFFEE57286B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{557A26C6-F21E-4F13-8F97-2AB80881C4B7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="8" xr2:uid="{557A26C6-F21E-4F13-8F97-2AB80881C4B7}"/>
   </bookViews>
   <sheets>
     <sheet name="Пример" sheetId="1" r:id="rId1"/>
@@ -2950,7 +2950,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5236" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5239" uniqueCount="469">
   <si>
     <t>DL 11.02</t>
   </si>
@@ -4373,6 +4373,15 @@
   <si>
     <t>RKA Leading avg</t>
   </si>
+  <si>
+    <t>general distr trade avg</t>
+  </si>
+  <si>
+    <t>general execution avg</t>
+  </si>
+  <si>
+    <t>general rka avg</t>
+  </si>
 </sst>
 </file>
 
@@ -5609,7 +5618,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="407">
+  <cellXfs count="410">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -6429,18 +6438,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -6471,7 +6468,19 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -6531,6 +6540,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -6546,9 +6558,11 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal 2" xfId="2" xr:uid="{0BF699D7-947A-4C7B-97F9-AAD9F375786C}"/>
@@ -7873,25 +7887,25 @@
       </c>
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
-      <c r="I1" s="371" t="s">
+      <c r="I1" s="367" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="372"/>
-      <c r="K1" s="372"/>
-      <c r="L1" s="372"/>
-      <c r="M1" s="372"/>
-      <c r="N1" s="372"/>
-      <c r="O1" s="372"/>
-      <c r="P1" s="372"/>
-      <c r="Q1" s="372"/>
-      <c r="R1" s="372"/>
-      <c r="S1" s="373"/>
-      <c r="T1" s="371" t="s">
+      <c r="J1" s="368"/>
+      <c r="K1" s="368"/>
+      <c r="L1" s="368"/>
+      <c r="M1" s="368"/>
+      <c r="N1" s="368"/>
+      <c r="O1" s="368"/>
+      <c r="P1" s="368"/>
+      <c r="Q1" s="368"/>
+      <c r="R1" s="368"/>
+      <c r="S1" s="369"/>
+      <c r="T1" s="367" t="s">
         <v>2</v>
       </c>
-      <c r="U1" s="372"/>
-      <c r="V1" s="372"/>
-      <c r="W1" s="373"/>
+      <c r="U1" s="368"/>
+      <c r="V1" s="368"/>
+      <c r="W1" s="369"/>
     </row>
     <row r="2" spans="1:23" s="77" customFormat="1" ht="59.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="I2" s="78" t="s">
@@ -7927,12 +7941,12 @@
       <c r="S2" s="80" t="s">
         <v>5</v>
       </c>
-      <c r="T2" s="374" t="s">
+      <c r="T2" s="370" t="s">
         <v>6</v>
       </c>
-      <c r="U2" s="375"/>
-      <c r="V2" s="375"/>
-      <c r="W2" s="376"/>
+      <c r="U2" s="371"/>
+      <c r="V2" s="371"/>
+      <c r="W2" s="372"/>
     </row>
     <row r="3" spans="1:23" s="87" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="81" t="s">
@@ -8020,10 +8034,10 @@
       </c>
       <c r="E4" s="91"/>
       <c r="F4" s="91"/>
-      <c r="G4" s="377">
+      <c r="G4" s="373">
         <v>2</v>
       </c>
-      <c r="H4" s="377">
+      <c r="H4" s="373">
         <v>1</v>
       </c>
       <c r="I4" s="92">
@@ -8057,8 +8071,8 @@
       <c r="D5" s="97" t="s">
         <v>68</v>
       </c>
-      <c r="G5" s="378"/>
-      <c r="H5" s="378"/>
+      <c r="G5" s="374"/>
+      <c r="H5" s="374"/>
       <c r="I5" s="98">
         <v>13101834.389945012</v>
       </c>
@@ -8077,8 +8091,8 @@
       <c r="D6" s="97" t="s">
         <v>68</v>
       </c>
-      <c r="G6" s="378"/>
-      <c r="H6" s="378"/>
+      <c r="G6" s="374"/>
+      <c r="H6" s="374"/>
       <c r="I6" s="98">
         <v>12765397.916910024</v>
       </c>
@@ -8097,8 +8111,8 @@
       <c r="D7" s="97" t="s">
         <v>68</v>
       </c>
-      <c r="G7" s="378"/>
-      <c r="H7" s="378"/>
+      <c r="G7" s="374"/>
+      <c r="H7" s="374"/>
       <c r="I7" s="98">
         <v>9760270.0104750115</v>
       </c>
@@ -8117,8 +8131,8 @@
       <c r="D8" s="97" t="s">
         <v>68</v>
       </c>
-      <c r="G8" s="378"/>
-      <c r="H8" s="378"/>
+      <c r="G8" s="374"/>
+      <c r="H8" s="374"/>
       <c r="I8" s="98">
         <v>14278538.622679975</v>
       </c>
@@ -8137,8 +8151,8 @@
       <c r="D9" s="97" t="s">
         <v>68</v>
       </c>
-      <c r="G9" s="378"/>
-      <c r="H9" s="378"/>
+      <c r="G9" s="374"/>
+      <c r="H9" s="374"/>
       <c r="I9" s="98">
         <v>18179410.183660042</v>
       </c>
@@ -8159,8 +8173,8 @@
       </c>
       <c r="E10" s="103"/>
       <c r="F10" s="103"/>
-      <c r="G10" s="379"/>
-      <c r="H10" s="379"/>
+      <c r="G10" s="375"/>
+      <c r="H10" s="375"/>
       <c r="I10" s="104">
         <v>10226726.025295002</v>
       </c>
@@ -8194,7 +8208,7 @@
       </c>
       <c r="E11" s="91"/>
       <c r="F11" s="91"/>
-      <c r="G11" s="377">
+      <c r="G11" s="373">
         <v>1</v>
       </c>
       <c r="H11" s="91"/>
@@ -8227,7 +8241,7 @@
       <c r="D12" s="96" t="s">
         <v>75</v>
       </c>
-      <c r="G12" s="378"/>
+      <c r="G12" s="374"/>
       <c r="I12" s="98"/>
       <c r="W12" s="99"/>
     </row>
@@ -8244,7 +8258,7 @@
       <c r="D13" s="96" t="s">
         <v>75</v>
       </c>
-      <c r="G13" s="378"/>
+      <c r="G13" s="374"/>
       <c r="I13" s="98"/>
       <c r="W13" s="99"/>
     </row>
@@ -8261,7 +8275,7 @@
       <c r="D14" s="96" t="s">
         <v>75</v>
       </c>
-      <c r="G14" s="378"/>
+      <c r="G14" s="374"/>
       <c r="I14" s="98"/>
       <c r="W14" s="99"/>
     </row>
@@ -8278,7 +8292,7 @@
       <c r="D15" s="96" t="s">
         <v>75</v>
       </c>
-      <c r="G15" s="378"/>
+      <c r="G15" s="374"/>
       <c r="I15" s="98"/>
       <c r="T15" s="98">
         <v>3407072.5562050003</v>
@@ -8300,7 +8314,7 @@
       <c r="D16" s="96" t="s">
         <v>75</v>
       </c>
-      <c r="G16" s="378"/>
+      <c r="G16" s="374"/>
       <c r="I16" s="98"/>
       <c r="T16" s="98"/>
       <c r="U16" s="98"/>
@@ -8322,7 +8336,7 @@
       </c>
       <c r="E17" s="103"/>
       <c r="F17" s="103"/>
-      <c r="G17" s="379"/>
+      <c r="G17" s="375"/>
       <c r="H17" s="103"/>
       <c r="I17" s="104"/>
       <c r="J17" s="103"/>
@@ -8355,7 +8369,7 @@
       </c>
       <c r="E18" s="91"/>
       <c r="F18" s="91"/>
-      <c r="G18" s="377">
+      <c r="G18" s="373">
         <v>1</v>
       </c>
       <c r="H18" s="91"/>
@@ -8388,7 +8402,7 @@
       <c r="D19" s="96" t="s">
         <v>77</v>
       </c>
-      <c r="G19" s="378"/>
+      <c r="G19" s="374"/>
       <c r="T19" s="98"/>
       <c r="U19" s="98"/>
       <c r="V19" s="98"/>
@@ -8407,7 +8421,7 @@
       <c r="D20" s="96" t="s">
         <v>77</v>
       </c>
-      <c r="G20" s="378"/>
+      <c r="G20" s="374"/>
       <c r="T20" s="98"/>
       <c r="U20" s="98"/>
       <c r="V20" s="98"/>
@@ -8426,7 +8440,7 @@
       <c r="D21" s="96" t="s">
         <v>77</v>
       </c>
-      <c r="G21" s="378"/>
+      <c r="G21" s="374"/>
       <c r="T21" s="98"/>
       <c r="U21" s="98"/>
       <c r="V21" s="98"/>
@@ -8445,7 +8459,7 @@
       <c r="D22" s="96" t="s">
         <v>77</v>
       </c>
-      <c r="G22" s="378"/>
+      <c r="G22" s="374"/>
       <c r="T22" s="98">
         <v>10871466.066474997</v>
       </c>
@@ -8466,7 +8480,7 @@
       <c r="D23" s="96" t="s">
         <v>77</v>
       </c>
-      <c r="G23" s="378"/>
+      <c r="G23" s="374"/>
       <c r="W23" s="99"/>
     </row>
     <row r="24" spans="1:23" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -8484,7 +8498,7 @@
       </c>
       <c r="E24" s="103"/>
       <c r="F24" s="103"/>
-      <c r="G24" s="379"/>
+      <c r="G24" s="375"/>
       <c r="H24" s="103"/>
       <c r="I24" s="103"/>
       <c r="J24" s="103"/>
@@ -8515,7 +8529,7 @@
       </c>
       <c r="E25" s="91"/>
       <c r="F25" s="91"/>
-      <c r="G25" s="377">
+      <c r="G25" s="373">
         <v>2</v>
       </c>
       <c r="H25" s="91"/>
@@ -8548,7 +8562,7 @@
       <c r="D26" s="96" t="s">
         <v>78</v>
       </c>
-      <c r="G26" s="378"/>
+      <c r="G26" s="374"/>
       <c r="K26" s="142" t="s">
         <v>80</v>
       </c>
@@ -8566,7 +8580,7 @@
       <c r="D27" s="96" t="s">
         <v>78</v>
       </c>
-      <c r="G27" s="378"/>
+      <c r="G27" s="374"/>
       <c r="K27" s="142" t="s">
         <v>81</v>
       </c>
@@ -8584,7 +8598,7 @@
       <c r="D28" s="96" t="s">
         <v>78</v>
       </c>
-      <c r="G28" s="378"/>
+      <c r="G28" s="374"/>
       <c r="K28" s="142" t="s">
         <v>82</v>
       </c>
@@ -8602,7 +8616,7 @@
       <c r="D29" s="96" t="s">
         <v>78</v>
       </c>
-      <c r="G29" s="378"/>
+      <c r="G29" s="374"/>
       <c r="K29" s="142" t="s">
         <v>83</v>
       </c>
@@ -8620,7 +8634,7 @@
       <c r="D30" s="96" t="s">
         <v>78</v>
       </c>
-      <c r="G30" s="378"/>
+      <c r="G30" s="374"/>
       <c r="K30" s="142" t="s">
         <v>84</v>
       </c>
@@ -8638,7 +8652,7 @@
       <c r="D31" s="101" t="s">
         <v>78</v>
       </c>
-      <c r="G31" s="379"/>
+      <c r="G31" s="375"/>
       <c r="K31" s="142" t="s">
         <v>85</v>
       </c>
@@ -8660,7 +8674,7 @@
       </c>
       <c r="E32" s="91"/>
       <c r="F32" s="91"/>
-      <c r="G32" s="377">
+      <c r="G32" s="373">
         <v>3</v>
       </c>
       <c r="H32" s="91"/>
@@ -8695,7 +8709,7 @@
       <c r="D33" s="96" t="s">
         <v>86</v>
       </c>
-      <c r="G33" s="378"/>
+      <c r="G33" s="374"/>
       <c r="J33" s="94" t="s">
         <v>88</v>
       </c>
@@ -8716,7 +8730,7 @@
       <c r="D34" s="96" t="s">
         <v>86</v>
       </c>
-      <c r="G34" s="378"/>
+      <c r="G34" s="374"/>
       <c r="J34" s="94" t="s">
         <v>89</v>
       </c>
@@ -8737,7 +8751,7 @@
       <c r="D35" s="96" t="s">
         <v>86</v>
       </c>
-      <c r="G35" s="378"/>
+      <c r="G35" s="374"/>
       <c r="J35" s="94" t="s">
         <v>90</v>
       </c>
@@ -8758,7 +8772,7 @@
       <c r="D36" s="96" t="s">
         <v>86</v>
       </c>
-      <c r="G36" s="378"/>
+      <c r="G36" s="374"/>
       <c r="J36" s="94" t="s">
         <v>91</v>
       </c>
@@ -8779,7 +8793,7 @@
       <c r="D37" s="96" t="s">
         <v>86</v>
       </c>
-      <c r="G37" s="378"/>
+      <c r="G37" s="374"/>
       <c r="J37" s="94" t="s">
         <v>92</v>
       </c>
@@ -8802,7 +8816,7 @@
       </c>
       <c r="E38" s="103"/>
       <c r="F38" s="103"/>
-      <c r="G38" s="379"/>
+      <c r="G38" s="375"/>
       <c r="H38" s="103"/>
       <c r="I38" s="103"/>
       <c r="J38" s="103" t="s">
@@ -8836,17 +8850,17 @@
       <c r="D40" s="115" t="s">
         <v>95</v>
       </c>
-      <c r="E40" s="380">
+      <c r="E40" s="376">
         <v>1</v>
       </c>
-      <c r="F40" s="381">
+      <c r="F40" s="378">
         <v>1</v>
       </c>
-      <c r="G40" s="381">
+      <c r="G40" s="378">
         <f>3+6+5</f>
         <v>14</v>
       </c>
-      <c r="H40" s="381">
+      <c r="H40" s="378">
         <v>1</v>
       </c>
       <c r="I40" s="91"/>
@@ -8900,10 +8914,10 @@
       <c r="D41" s="109" t="s">
         <v>95</v>
       </c>
-      <c r="E41" s="367"/>
-      <c r="F41" s="368"/>
-      <c r="G41" s="368"/>
-      <c r="H41" s="368"/>
+      <c r="E41" s="377"/>
+      <c r="F41" s="379"/>
+      <c r="G41" s="379"/>
+      <c r="H41" s="379"/>
       <c r="M41" s="123" t="s">
         <v>103</v>
       </c>
@@ -8949,17 +8963,17 @@
       <c r="D42" s="109" t="s">
         <v>109</v>
       </c>
-      <c r="E42" s="367">
+      <c r="E42" s="377">
         <v>1</v>
       </c>
-      <c r="F42" s="368">
+      <c r="F42" s="379">
         <v>1</v>
       </c>
-      <c r="G42" s="368">
+      <c r="G42" s="379">
         <f>3+7+5</f>
         <v>15</v>
       </c>
-      <c r="H42" s="368">
+      <c r="H42" s="379">
         <v>1</v>
       </c>
       <c r="M42" s="129" t="s">
@@ -9009,10 +9023,10 @@
       <c r="D43" s="109" t="s">
         <v>109</v>
       </c>
-      <c r="E43" s="367"/>
-      <c r="F43" s="368"/>
-      <c r="G43" s="368"/>
-      <c r="H43" s="368"/>
+      <c r="E43" s="377"/>
+      <c r="F43" s="379"/>
+      <c r="G43" s="379"/>
+      <c r="H43" s="379"/>
       <c r="M43" s="129" t="s">
         <v>117</v>
       </c>
@@ -9116,17 +9130,17 @@
       <c r="D45" s="109" t="s">
         <v>131</v>
       </c>
-      <c r="E45" s="367">
+      <c r="E45" s="377">
         <v>1</v>
       </c>
-      <c r="F45" s="368">
+      <c r="F45" s="379">
         <v>1</v>
       </c>
-      <c r="G45" s="368">
+      <c r="G45" s="379">
         <f>6+7+5</f>
         <v>18</v>
       </c>
-      <c r="H45" s="368">
+      <c r="H45" s="379">
         <v>1</v>
       </c>
       <c r="M45" s="129" t="s">
@@ -9172,10 +9186,10 @@
       <c r="D46" s="135" t="s">
         <v>131</v>
       </c>
-      <c r="E46" s="370"/>
-      <c r="F46" s="369"/>
-      <c r="G46" s="369"/>
-      <c r="H46" s="369"/>
+      <c r="E46" s="381"/>
+      <c r="F46" s="380"/>
+      <c r="G46" s="380"/>
+      <c r="H46" s="380"/>
       <c r="I46" s="103"/>
       <c r="J46" s="103"/>
       <c r="K46" s="103"/>
@@ -9214,6 +9228,14 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="E42:E43"/>
+    <mergeCell ref="F42:F43"/>
+    <mergeCell ref="G42:G43"/>
+    <mergeCell ref="H42:H43"/>
+    <mergeCell ref="H45:H46"/>
+    <mergeCell ref="G45:G46"/>
+    <mergeCell ref="F45:F46"/>
+    <mergeCell ref="E45:E46"/>
     <mergeCell ref="T1:W1"/>
     <mergeCell ref="T2:W2"/>
     <mergeCell ref="G32:G38"/>
@@ -9227,14 +9249,6 @@
     <mergeCell ref="G4:G10"/>
     <mergeCell ref="H4:H10"/>
     <mergeCell ref="I1:S1"/>
-    <mergeCell ref="E42:E43"/>
-    <mergeCell ref="F42:F43"/>
-    <mergeCell ref="G42:G43"/>
-    <mergeCell ref="H42:H43"/>
-    <mergeCell ref="H45:H46"/>
-    <mergeCell ref="G45:G46"/>
-    <mergeCell ref="F45:F46"/>
-    <mergeCell ref="E45:E46"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -51548,8 +51562,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7BCE706-FAD7-4CD7-B4ED-991E63946BE0}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:AX68"/>
+  <dimension ref="A1:BA68"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25" bestFit="1" customWidth="1"/>
@@ -51583,12 +51596,10 @@
     <col min="40" max="40" width="14.5703125" customWidth="1"/>
     <col min="41" max="41" width="21.42578125" customWidth="1"/>
     <col min="42" max="42" width="15.42578125" customWidth="1"/>
-    <col min="43" max="43" width="15.5703125" customWidth="1"/>
-    <col min="46" max="46" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="43" max="53" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:53" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
@@ -51612,7 +51623,7 @@
       <c r="U1" s="398" t="s">
         <v>1</v>
       </c>
-      <c r="V1" s="401"/>
+      <c r="V1" s="402"/>
       <c r="W1" s="362"/>
       <c r="X1" s="362"/>
       <c r="Y1" s="362"/>
@@ -51627,7 +51638,7 @@
       </c>
       <c r="AG1" s="362"/>
       <c r="AH1" s="362"/>
-      <c r="AI1" s="402"/>
+      <c r="AI1" s="403"/>
       <c r="AJ1" s="362"/>
       <c r="AK1" s="362"/>
       <c r="AL1" s="362"/>
@@ -51636,7 +51647,7 @@
       <c r="AO1" s="362"/>
       <c r="AP1" s="363"/>
     </row>
-    <row r="2" spans="1:50" ht="58.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:53" ht="58.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -51658,15 +51669,15 @@
       <c r="M2" s="400"/>
       <c r="N2" s="400"/>
       <c r="O2" s="400"/>
-      <c r="P2" s="406"/>
+      <c r="P2" s="401"/>
       <c r="Q2" s="399" t="s">
         <v>3</v>
       </c>
-      <c r="R2" s="403"/>
-      <c r="S2" s="403"/>
-      <c r="T2" s="403"/>
-      <c r="U2" s="403"/>
-      <c r="V2" s="404"/>
+      <c r="R2" s="404"/>
+      <c r="S2" s="404"/>
+      <c r="T2" s="404"/>
+      <c r="U2" s="404"/>
+      <c r="V2" s="405"/>
       <c r="W2" s="227" t="s">
         <v>4</v>
       </c>
@@ -51699,7 +51710,7 @@
       </c>
       <c r="AG2" s="366"/>
       <c r="AH2" s="366"/>
-      <c r="AI2" s="405"/>
+      <c r="AI2" s="406"/>
       <c r="AJ2" s="366"/>
       <c r="AK2" s="366"/>
       <c r="AL2" s="366"/>
@@ -51722,9 +51733,9 @@
       <c r="AU2" s="400"/>
       <c r="AV2" s="400"/>
       <c r="AW2" s="400"/>
-      <c r="AX2" s="406"/>
-    </row>
-    <row r="3" spans="1:50" ht="45.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="AX2" s="401"/>
+    </row>
+    <row r="3" spans="1:53" ht="45.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>8</v>
       </c>
@@ -51851,32 +51862,41 @@
       <c r="AP3" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="AQ3" s="279" t="s">
+      <c r="AQ3" s="407" t="s">
         <v>458</v>
       </c>
-      <c r="AR3" s="279" t="s">
+      <c r="AR3" s="407" t="s">
         <v>459</v>
       </c>
-      <c r="AS3" s="279" t="s">
+      <c r="AS3" s="407" t="s">
         <v>460</v>
       </c>
-      <c r="AT3" s="279" t="s">
+      <c r="AT3" s="407" t="s">
         <v>461</v>
       </c>
-      <c r="AU3" s="279" t="s">
+      <c r="AU3" s="407" t="s">
         <v>462</v>
       </c>
-      <c r="AV3" s="279" t="s">
+      <c r="AV3" s="407" t="s">
         <v>463</v>
       </c>
-      <c r="AW3" s="279" t="s">
+      <c r="AW3" s="407" t="s">
         <v>464</v>
       </c>
-      <c r="AX3" s="279" t="s">
+      <c r="AX3" s="407" t="s">
         <v>465</v>
       </c>
-    </row>
-    <row r="4" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
+      <c r="AY3" s="407" t="s">
+        <v>468</v>
+      </c>
+      <c r="AZ3" s="407" t="s">
+        <v>466</v>
+      </c>
+      <c r="BA3" s="407" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="4" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>412</v>
       </c>
@@ -51973,40 +51993,52 @@
         <v>1119300</v>
       </c>
       <c r="AP4" s="224"/>
-      <c r="AQ4" s="218">
+      <c r="AQ4" s="408">
         <f>AVERAGE(I:I)</f>
         <v>21487211.718153846</v>
       </c>
-      <c r="AR4">
+      <c r="AR4" s="409">
         <f>AVERAGE(J:J)</f>
         <v>10927566.909846151</v>
       </c>
-      <c r="AS4">
+      <c r="AS4" s="409">
         <f>AVERAGE(K:K)</f>
         <v>45980000.465384625</v>
       </c>
-      <c r="AT4">
+      <c r="AT4" s="409">
         <f>AVERAGE(L:L)</f>
         <v>262142098.28921932</v>
       </c>
-      <c r="AU4">
+      <c r="AU4" s="409">
         <f>AVERAGE(M:M)</f>
         <v>463863.97324550181</v>
       </c>
-      <c r="AV4">
+      <c r="AV4" s="409">
         <f>AVERAGE(M:M)</f>
         <v>463863.97324550181</v>
       </c>
-      <c r="AW4">
+      <c r="AW4" s="409">
         <f>AVERAGE(O:O)</f>
         <v>275303982.09645641</v>
       </c>
-      <c r="AX4" t="e">
+      <c r="AX4" s="409" t="e">
         <f>AVERAGE(P:P)</f>
         <v>#DIV/0!</v>
       </c>
-    </row>
-    <row r="5" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="AY4" s="408">
+        <f>AQ4</f>
+        <v>21487211.718153846</v>
+      </c>
+      <c r="AZ4" s="409">
+        <f>AVERAGE(J:J:K:K)</f>
+        <v>28453783.687615391</v>
+      </c>
+      <c r="BA4" s="409">
+        <f>AVERAGE(L:L,M:M,N:N,O:O,P:P)</f>
+        <v>201831632.15526024</v>
+      </c>
+    </row>
+    <row r="5" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>412</v>
       </c>
@@ -52107,7 +52139,7 @@
       <c r="AP5" s="224"/>
       <c r="AQ5" s="218"/>
     </row>
-    <row r="6" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>418</v>
       </c>
@@ -52208,7 +52240,7 @@
       <c r="AP6" s="224"/>
       <c r="AQ6" s="218"/>
     </row>
-    <row r="7" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>420</v>
       </c>
@@ -52309,7 +52341,7 @@
       <c r="AP7" s="224"/>
       <c r="AQ7" s="218"/>
     </row>
-    <row r="8" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>421</v>
       </c>
@@ -52410,7 +52442,7 @@
       <c r="AP8" s="224"/>
       <c r="AQ8" s="218"/>
     </row>
-    <row r="9" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>421</v>
       </c>
@@ -52517,7 +52549,7 @@
       <c r="AP9" s="224"/>
       <c r="AQ9" s="218"/>
     </row>
-    <row r="10" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>420</v>
       </c>
@@ -52621,7 +52653,7 @@
       <c r="AP10" s="239"/>
       <c r="AQ10" s="218"/>
     </row>
-    <row r="11" spans="1:50" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>423</v>
       </c>
@@ -52726,7 +52758,7 @@
       <c r="AP11" s="239"/>
       <c r="AQ11" s="218"/>
     </row>
-    <row r="12" spans="1:50" s="239" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:53" s="239" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>426</v>
       </c>
@@ -52835,7 +52867,7 @@
       <c r="AP12" s="224"/>
       <c r="AQ12" s="218"/>
     </row>
-    <row r="13" spans="1:50" s="239" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:53" s="239" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>426</v>
       </c>
@@ -52944,7 +52976,7 @@
       <c r="AP13" s="224"/>
       <c r="AQ13" s="218"/>
     </row>
-    <row r="14" spans="1:50" s="239" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:53" s="239" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>428</v>
       </c>
@@ -53055,7 +53087,7 @@
       <c r="AP14" s="224"/>
       <c r="AQ14" s="218"/>
     </row>
-    <row r="15" spans="1:50" s="239" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:53" s="239" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>429</v>
       </c>
@@ -53164,7 +53196,7 @@
       <c r="AP15" s="224"/>
       <c r="AQ15" s="218"/>
     </row>
-    <row r="16" spans="1:50" s="239" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:53" s="239" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>429</v>
       </c>
@@ -53491,7 +53523,7 @@
       <c r="AP18" s="224"/>
       <c r="AQ18" s="218"/>
     </row>
-    <row r="19" spans="1:43" s="239" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:43" s="239" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>430</v>
       </c>
@@ -53600,7 +53632,7 @@
       <c r="AP19" s="224"/>
       <c r="AQ19" s="218"/>
     </row>
-    <row r="20" spans="1:43" s="239" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:43" s="239" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>432</v>
       </c>
@@ -53707,7 +53739,7 @@
       <c r="AP20" s="224"/>
       <c r="AQ20" s="218"/>
     </row>
-    <row r="21" spans="1:43" s="239" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:43" s="239" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>432</v>
       </c>
@@ -53813,7 +53845,7 @@
       <c r="AO21"/>
       <c r="AQ21" s="218"/>
     </row>
-    <row r="22" spans="1:43" s="239" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:43" s="239" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>432</v>
       </c>
@@ -53922,7 +53954,7 @@
       <c r="AP22" s="224"/>
       <c r="AQ22" s="218"/>
     </row>
-    <row r="23" spans="1:43" s="239" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:43" s="239" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>432</v>
       </c>
@@ -54029,7 +54061,7 @@
       <c r="AP23" s="224"/>
       <c r="AQ23" s="218"/>
     </row>
-    <row r="24" spans="1:43" s="239" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:43" s="239" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>432</v>
       </c>
@@ -54247,7 +54279,7 @@
       <c r="AP25" s="224"/>
       <c r="AQ25" s="218"/>
     </row>
-    <row r="26" spans="1:43" s="239" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:43" s="239" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>433</v>
       </c>
@@ -54465,7 +54497,7 @@
       <c r="AP27" s="224"/>
       <c r="AQ27" s="218"/>
     </row>
-    <row r="28" spans="1:43" s="239" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:43" s="239" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>435</v>
       </c>
@@ -54574,7 +54606,7 @@
       <c r="AP28" s="224"/>
       <c r="AQ28" s="218"/>
     </row>
-    <row r="29" spans="1:43" s="239" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:43" s="239" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>435</v>
       </c>
@@ -54792,7 +54824,7 @@
       <c r="AP30" s="224"/>
       <c r="AQ30" s="218"/>
     </row>
-    <row r="31" spans="1:43" s="239" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:43" s="239" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>433</v>
       </c>
@@ -54901,7 +54933,7 @@
       <c r="AP31" s="224"/>
       <c r="AQ31" s="218"/>
     </row>
-    <row r="32" spans="1:43" s="239" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:43" s="239" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>433</v>
       </c>
@@ -55205,7 +55237,7 @@
       <c r="AO34"/>
       <c r="AQ34" s="218"/>
     </row>
-    <row r="35" spans="1:43" s="239" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:43" s="239" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>242</v>
       </c>
@@ -55297,7 +55329,7 @@
       <c r="AO35"/>
       <c r="AQ35" s="218"/>
     </row>
-    <row r="36" spans="1:43" s="239" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:43" s="239" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>418</v>
       </c>
@@ -55402,7 +55434,7 @@
       <c r="AP36" s="224"/>
       <c r="AQ36" s="218"/>
     </row>
-    <row r="37" spans="1:43" s="239" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:43" s="239" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>432</v>
       </c>
@@ -55616,7 +55648,7 @@
       <c r="AP38" s="224"/>
       <c r="AQ38" s="218"/>
     </row>
-    <row r="39" spans="1:43" s="239" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:43" s="239" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>191</v>
       </c>
@@ -55725,7 +55757,7 @@
       <c r="AP39" s="224"/>
       <c r="AQ39" s="218"/>
     </row>
-    <row r="40" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>191</v>
       </c>
@@ -55826,7 +55858,7 @@
       <c r="AP40" s="224"/>
       <c r="AQ40" s="218"/>
     </row>
-    <row r="41" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>438</v>
       </c>
@@ -55927,7 +55959,7 @@
       <c r="AP41" s="224"/>
       <c r="AQ41" s="218"/>
     </row>
-    <row r="42" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>438</v>
       </c>
@@ -56028,7 +56060,7 @@
       <c r="AP42" s="239"/>
       <c r="AQ42" s="218"/>
     </row>
-    <row r="43" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>412</v>
       </c>
@@ -56109,7 +56141,7 @@
       </c>
       <c r="AQ43" s="218"/>
     </row>
-    <row r="44" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>421</v>
       </c>
@@ -56188,7 +56220,7 @@
       <c r="AP44" s="224"/>
       <c r="AQ44" s="218"/>
     </row>
-    <row r="45" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>420</v>
       </c>
@@ -56272,7 +56304,7 @@
       </c>
       <c r="AQ45" s="218"/>
     </row>
-    <row r="46" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>429</v>
       </c>
@@ -56354,7 +56386,7 @@
       <c r="AP46" s="224"/>
       <c r="AQ46" s="218"/>
     </row>
-    <row r="47" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>430</v>
       </c>
@@ -56437,7 +56469,7 @@
       </c>
       <c r="AQ47" s="218"/>
     </row>
-    <row r="48" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>430</v>
       </c>
@@ -56518,7 +56550,7 @@
       </c>
       <c r="AQ48" s="218"/>
     </row>
-    <row r="49" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>434</v>
       </c>
@@ -56597,7 +56629,7 @@
       <c r="AP49" s="224"/>
       <c r="AQ49" s="218"/>
     </row>
-    <row r="50" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>434</v>
       </c>
@@ -56674,7 +56706,7 @@
       <c r="AP50" s="224"/>
       <c r="AQ50" s="218"/>
     </row>
-    <row r="51" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>436</v>
       </c>
@@ -56753,7 +56785,7 @@
       <c r="AP51" s="224"/>
       <c r="AQ51" s="218"/>
     </row>
-    <row r="52" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>433</v>
       </c>
@@ -56832,7 +56864,7 @@
       <c r="AP52" s="224"/>
       <c r="AQ52" s="218"/>
     </row>
-    <row r="53" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>426</v>
       </c>
@@ -56911,7 +56943,7 @@
       <c r="AP53" s="224"/>
       <c r="AQ53" s="218"/>
     </row>
-    <row r="54" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>428</v>
       </c>
@@ -56991,7 +57023,7 @@
       <c r="AP54" s="224"/>
       <c r="AQ54" s="218"/>
     </row>
-    <row r="55" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>242</v>
       </c>
@@ -57070,7 +57102,7 @@
       <c r="AP55" s="224"/>
       <c r="AQ55" s="218"/>
     </row>
-    <row r="56" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>418</v>
       </c>
@@ -57149,7 +57181,7 @@
       <c r="AP56" s="224"/>
       <c r="AQ56" s="218"/>
     </row>
-    <row r="57" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>432</v>
       </c>
@@ -57231,7 +57263,7 @@
       <c r="AP57" s="224"/>
       <c r="AQ57" s="218"/>
     </row>
-    <row r="58" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>438</v>
       </c>
@@ -57313,7 +57345,7 @@
       <c r="AP58" s="224"/>
       <c r="AQ58" s="218"/>
     </row>
-    <row r="59" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>430</v>
       </c>
@@ -57394,7 +57426,7 @@
       </c>
       <c r="AQ59" s="218"/>
     </row>
-    <row r="60" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>242</v>
       </c>
@@ -57471,7 +57503,7 @@
       <c r="AP60" s="224"/>
       <c r="AQ60" s="218"/>
     </row>
-    <row r="61" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>432</v>
       </c>
@@ -57547,7 +57579,7 @@
       <c r="AP61" s="239"/>
       <c r="AQ61" s="218"/>
     </row>
-    <row r="62" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>242</v>
       </c>
@@ -57623,7 +57655,7 @@
       <c r="AP62" s="224"/>
       <c r="AQ62" s="218"/>
     </row>
-    <row r="63" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>420</v>
       </c>
@@ -57833,7 +57865,7 @@
       <c r="AP65" s="224"/>
       <c r="AQ65" s="218"/>
     </row>
-    <row r="66" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>421</v>
       </c>
@@ -57906,7 +57938,7 @@
       <c r="AP66" s="224"/>
       <c r="AQ66" s="218"/>
     </row>
-    <row r="67" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>438</v>
       </c>
@@ -57976,7 +58008,7 @@
       <c r="AP67" s="224"/>
       <c r="AQ67" s="218"/>
     </row>
-    <row r="68" spans="1:43" s="246" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:43" s="246" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="246" t="s">
         <v>434</v>
       </c>
@@ -58054,14 +58086,7 @@
       <c r="AQ68" s="218"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:AP68" xr:uid="{F4E271B0-9BC6-43A9-829F-67EBEF38B757}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="TSL NOR  SPb  North- Murmansk"/>
-        <filter val="TSL NOR Len Obl"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A3:AP68" xr:uid="{F4E271B0-9BC6-43A9-829F-67EBEF38B757}"/>
   <mergeCells count="9">
     <mergeCell ref="AR2:AS2"/>
     <mergeCell ref="AT2:AX2"/>
